--- a/src/main/resources/excel_data/UserTrailData.xlsx
+++ b/src/main/resources/excel_data/UserTrailData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishmitha G\Downloads\ctp-contiplus-web-qa-automation-java\ctp-contiplus-web-qa-automation-java\src\main\resources\excel_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishmitha G\Documents\Automation\ctp-contiplus-web-qa-automation-java\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83E7F06-457E-49F9-9179-F6FD7E3359DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D026F6-A8AB-4A17-AA37-B7A5D9CD4019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,16 +49,16 @@
     <t>Customer Template</t>
   </si>
   <si>
-    <t>Bulk Upload 2</t>
-  </si>
-  <si>
-    <t>bulkimport2@maildrop.cc</t>
-  </si>
-  <si>
-    <t>pp</t>
-  </si>
-  <si>
-    <t>Templates1</t>
+    <t>Bulk Upload 20</t>
+  </si>
+  <si>
+    <t>vtesttemp1</t>
+  </si>
+  <si>
+    <t>2customTemplate</t>
+  </si>
+  <si>
+    <t>bulkimport6@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -110,10 +110,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -429,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -477,17 +480,21 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
